--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9501bda68bb04d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d6b5e1904b44fbc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d6b5e1904b44fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re25fc8dbad0d4e55"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re25fc8dbad0d4e55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1432ce44070443f5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1432ce44070443f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7ea2ada4e634053"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7ea2ada4e634053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29c1d1f75ac941c1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29c1d1f75ac941c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38ec99c37c1f4586"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38ec99c37c1f4586"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R454fc22200b3484b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R454fc22200b3484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bd366f5ee364ec6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bd366f5ee364ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f066bde41204fbd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f066bde41204fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R61f83e5fe49443ed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R61f83e5fe49443ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68ecb6620bc14373"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68ecb6620bc14373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd90bc099e6024c68"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd90bc099e6024c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27320fbf18114c82"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R27320fbf18114c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69756456b51943ce"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69756456b51943ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R391a87518a4840fa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R391a87518a4840fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5baa02de6174fed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_UniqueValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5baa02de6174fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde5652a161434cf9"/>
   </x:sheets>
 </x:workbook>
 </file>
